--- a/AAII_Financials/Yearly/ZSQR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZSQR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>ZSQR</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -801,11 +801,11 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>6700</v>
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -855,8 +855,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>200</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -883,10 +883,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -920,10 +920,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10100</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>3</v>
@@ -947,10 +947,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-10100</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
-        <v>-21500</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -986,11 +986,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-300</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1014,10 +1014,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-9200</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>-20200</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -1040,11 +1040,11 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>100</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1068,10 +1068,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-10900</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>-21300</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -1149,10 +1149,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-10900</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>-21300</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -1176,10 +1176,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-9800</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>-21300</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -1310,11 +1310,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>300</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -1338,10 +1338,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-9800</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>-21300</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -1392,10 +1392,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-9800</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>-21300</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
@@ -1476,11 +1476,11 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>500</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1500</v>
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1533,8 +1533,8 @@
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1611,11 +1611,11 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E46" s="3">
-        <v>1700</v>
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1638,8 +1638,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>5700</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -1665,11 +1665,11 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>100</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1693,7 +1693,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -1773,11 +1773,11 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2700</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1827,11 +1827,11 @@
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>8900</v>
-      </c>
-      <c r="E54" s="3">
-        <v>4600</v>
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -1880,11 +1880,11 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1400</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -1908,10 +1908,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -1935,10 +1935,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -1962,10 +1962,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="E60" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -1989,10 +1989,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2015,11 +2015,11 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2124,10 +2124,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="E66" s="3">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2272,10 +2272,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-98200</v>
+        <v>0</v>
       </c>
       <c r="E72" s="3">
-        <v>-87400</v>
+        <v>0</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2380,10 +2380,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="E76" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2466,10 +2466,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-9800</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>-21300</v>
+        <v>0</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -2505,11 +2505,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2668,10 +2668,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-6600</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>-7200</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -2936,11 +2936,11 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>5700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>4900</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -2991,10 +2991,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
